--- a/download/NeuroCLI_Karsilastirma_Matrisi_2026.xlsx
+++ b/download/NeuroCLI_Karsilastirma_Matrisi_2026.xlsx
@@ -82,13 +82,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00198754"/>
+      <color rgb="006c757d"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="006c757d"/>
+      <color rgb="00198754"/>
       <sz val="12"/>
     </font>
     <font>
@@ -239,13 +239,13 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1696,9 +1696,9 @@
           <t>Tree-sitter Entegrasyonu</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -2254,9 +2254,9 @@
           <t>Tarayıcı Otomasyonu</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
@@ -2750,9 +2750,9 @@
           <t>Planlı Görevler / Scheduled Tasks</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -3184,9 +3184,9 @@
           <t>SKILL.md Standardı (YAML Frontmatter)</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>⚠️</t>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -3308,9 +3308,9 @@
           <t>Skill Paylaşımı (GitHub Registry)</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -3432,9 +3432,9 @@
           <t>AGENTS.md Evrensel Standardı</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>⚠️</t>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -3494,9 +3494,9 @@
           <t>agentskills.io Spec Uyumu</t>
         </is>
       </c>
-      <c r="C47" s="10" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -3680,9 +3680,9 @@
           <t>Plugin Bundle (Skills+Hooks+MCP)</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>⚠️</t>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -5292,9 +5292,9 @@
           <t>GitHub PR/Issue İşlemleri</t>
         </is>
       </c>
-      <c r="C76" s="9" t="inlineStr">
-        <is>
-          <t>⚠️</t>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
@@ -5416,9 +5416,9 @@
           <t>CI/CD Pipeline Entegrasyonu</t>
         </is>
       </c>
-      <c r="C78" s="10" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
@@ -5726,9 +5726,9 @@
           <t>Linting Entegrasyonu</t>
         </is>
       </c>
-      <c r="C83" s="10" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
@@ -5788,9 +5788,9 @@
           <t>Test Çalıştırma Entegrasyonu</t>
         </is>
       </c>
-      <c r="C84" s="10" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
@@ -5850,9 +5850,9 @@
           <t>Kod İnceleme (Review)</t>
         </is>
       </c>
-      <c r="C85" s="10" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
@@ -5974,9 +5974,9 @@
           <t>Güvenlik Tarama</t>
         </is>
       </c>
-      <c r="C87" s="10" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
@@ -6346,9 +6346,9 @@
           <t>Auto Mod (Tam Otonom)</t>
         </is>
       </c>
-      <c r="C93" s="10" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
@@ -6408,9 +6408,9 @@
           <t>/goal / /routine Komutları</t>
         </is>
       </c>
-      <c r="C94" s="10" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
@@ -6470,9 +6470,9 @@
           <t>Paralel Agent Çalıştırma</t>
         </is>
       </c>
-      <c r="C95" s="10" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
@@ -6532,9 +6532,9 @@
           <t>Background Session</t>
         </is>
       </c>
-      <c r="C96" s="10" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>16.5</v>
@@ -6890,7 +6890,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>19.5</v>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>22.5</v>
@@ -7000,8 +7000,8 @@
           <t>Yetenek (Skill) Sistemi</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
-        <v>7.5</v>
+      <c r="B10" s="8" t="n">
+        <v>16.5</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>18</v>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>9</v>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>7.5</v>
+        <v>12</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>12</v>
@@ -7333,8 +7333,8 @@
           <t>Kod Kalitesi</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
-        <v>1.5</v>
+      <c r="B19" s="8" t="n">
+        <v>13.5</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>12</v>
@@ -7407,8 +7407,8 @@
           <t>Gelişmiş AI Özellikleri</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
-        <v>3</v>
+      <c r="B21" s="8" t="n">
+        <v>15</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>18</v>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>196.5</v>
+        <v>244.5</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>195</v>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>%69.7</t>
+          <t>%86.7</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
@@ -7540,37 +7540,37 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+      <c r="H24" s="18" t="inlineStr">
+        <is>
           <t>#3</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>#10</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>#6</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>#2</t>
         </is>
       </c>
       <c r="I24" s="17" t="inlineStr">
@@ -9155,40 +9155,40 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>Cursor CLI</t>
+          <t>NeuroCLI</t>
         </is>
       </c>
       <c r="B4" s="26" t="n">
-        <v>205.5</v>
+        <v>244.5</v>
       </c>
       <c r="C4" s="26" t="n">
-        <v>72.90000000000001</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>GitHub Copilot CLI</t>
+          <t>Cursor CLI</t>
         </is>
       </c>
       <c r="B5" s="26" t="n">
-        <v>198</v>
+        <v>205.5</v>
       </c>
       <c r="C5" s="26" t="n">
-        <v>70.2</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>NeuroCLI</t>
+          <t>GitHub Copilot CLI</t>
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>196.5</v>
+        <v>198</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>69.7</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="7">
